--- a/AAII_Financials/Quarterly/LAAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LAAB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>LAAB</t>
   </si>
@@ -656,118 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E7" s="2">
         <v>45169</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45077</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44985</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44895</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44804</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44712</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44620</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44530</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44439</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44347</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44255</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44165</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44074</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43982</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43890</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43799</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43708</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43616</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43524</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43434</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43343</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43251</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -840,8 +843,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -914,8 +920,11 @@
       <c r="Z9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1090,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1217,8 +1236,8 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
@@ -1232,14 +1251,17 @@
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1312,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,8 +1362,9 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1385,11 +1411,11 @@
         <v>0</v>
       </c>
       <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
         <v>38500</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
       <c r="T17" s="3">
         <v>0</v>
       </c>
@@ -1411,8 +1437,11 @@
       <c r="Z17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1459,11 +1488,11 @@
         <v>0</v>
       </c>
       <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
         <v>-38500</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
         <v>0</v>
       </c>
@@ -1485,8 +1514,11 @@
       <c r="Z18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,8 +1545,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1587,8 +1620,11 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1661,8 +1697,11 @@
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1706,37 +1745,40 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>4</v>
+      <c r="X22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1780,20 +1822,20 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-38500</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
         <v>0</v>
       </c>
@@ -1809,8 +1851,11 @@
       <c r="Z23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1883,8 +1928,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,8 +2005,11 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2002,20 +2053,20 @@
         <v>0</v>
       </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-38500</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
         <v>0</v>
       </c>
@@ -2031,8 +2082,11 @@
       <c r="Z26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2076,20 +2130,20 @@
         <v>0</v>
       </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-38500</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
         <v>0</v>
       </c>
@@ -2105,8 +2159,11 @@
       <c r="Z27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2220,11 +2280,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2253,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,8 +2467,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2475,8 +2544,11 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2520,20 +2592,20 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-38500</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
         <v>0</v>
       </c>
@@ -2549,8 +2621,11 @@
       <c r="Z33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,8 +2698,11 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2668,20 +2746,20 @@
         <v>0</v>
       </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-38500</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
         <v>0</v>
       </c>
@@ -2697,87 +2775,93 @@
       <c r="Z35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E38" s="2">
         <v>45169</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45077</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44985</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44895</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44804</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44712</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44620</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44530</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44439</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44347</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44255</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44165</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44074</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43982</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43890</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43799</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43708</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43616</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43524</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43434</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43343</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43251</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,8 +2917,9 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2906,8 +2992,11 @@
       <c r="Z41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2980,8 +3069,11 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3054,8 +3146,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3128,8 +3223,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3202,8 +3300,11 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3276,8 +3377,11 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3350,8 +3454,11 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3424,8 +3531,11 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3462,8 +3572,8 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
@@ -3480,8 +3590,8 @@
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3498,8 +3608,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,8 +3762,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3720,8 +3839,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,8 +3916,11 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3868,8 +3993,11 @@
       <c r="Z54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,8 +4053,9 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3998,8 +4128,11 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4054,8 +4187,8 @@
       <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
+      <c r="U58" s="3">
+        <v>100</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
@@ -4072,8 +4205,11 @@
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4087,7 +4223,7 @@
         <v>200</v>
       </c>
       <c r="G59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H59" s="3">
         <v>100</v>
@@ -4108,7 +4244,7 @@
         <v>100</v>
       </c>
       <c r="N59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
@@ -4129,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V59" s="3">
         <v>100</v>
@@ -4141,13 +4277,16 @@
         <v>100</v>
       </c>
       <c r="Y59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4167,7 +4306,7 @@
         <v>300</v>
       </c>
       <c r="I60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J60" s="3">
         <v>200</v>
@@ -4191,7 +4330,7 @@
         <v>200</v>
       </c>
       <c r="Q60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R60" s="3">
         <v>100</v>
@@ -4218,10 +4357,13 @@
         <v>100</v>
       </c>
       <c r="Z60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4294,8 +4436,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4368,8 +4513,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,8 +4744,11 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4611,7 +4768,7 @@
         <v>300</v>
       </c>
       <c r="I66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J66" s="3">
         <v>200</v>
@@ -4635,7 +4792,7 @@
         <v>200</v>
       </c>
       <c r="Q66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R66" s="3">
         <v>100</v>
@@ -4662,10 +4819,13 @@
         <v>100</v>
       </c>
       <c r="Z66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,8 +5158,11 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4997,7 +5170,7 @@
         <v>-39100</v>
       </c>
       <c r="E72" s="3">
-        <v>-39000</v>
+        <v>-39100</v>
       </c>
       <c r="F72" s="3">
         <v>-39000</v>
@@ -5015,7 +5188,7 @@
         <v>-39000</v>
       </c>
       <c r="K72" s="3">
-        <v>-38900</v>
+        <v>-39000</v>
       </c>
       <c r="L72" s="3">
         <v>-38900</v>
@@ -5033,13 +5206,13 @@
         <v>-38900</v>
       </c>
       <c r="Q72" s="3">
-        <v>-38800</v>
+        <v>-38900</v>
       </c>
       <c r="R72" s="3">
         <v>-38800</v>
       </c>
       <c r="S72" s="3">
-        <v>-200</v>
+        <v>-38800</v>
       </c>
       <c r="T72" s="3">
         <v>-200</v>
@@ -5051,7 +5224,7 @@
         <v>-200</v>
       </c>
       <c r="W72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="X72" s="3">
         <v>-100</v>
@@ -5062,8 +5235,11 @@
       <c r="Z72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,8 +5466,11 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -5305,7 +5490,7 @@
         <v>-300</v>
       </c>
       <c r="I76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="J76" s="3">
         <v>-200</v>
@@ -5329,7 +5514,7 @@
         <v>-200</v>
       </c>
       <c r="Q76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="R76" s="3">
         <v>-100</v>
@@ -5353,13 +5538,16 @@
         <v>-100</v>
       </c>
       <c r="Y76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,87 +5620,93 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E80" s="2">
         <v>45169</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45077</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44985</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44895</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44804</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44712</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44620</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44530</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44439</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44347</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44255</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44165</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44074</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43982</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43890</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43799</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43708</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43616</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43524</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43434</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43343</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43251</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5556,20 +5750,20 @@
         <v>0</v>
       </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-38500</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
         <v>0</v>
       </c>
@@ -5585,8 +5779,11 @@
       <c r="Z81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5687,8 +5885,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,8 +6270,11 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6131,8 +6347,11 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6378,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6233,8 +6453,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,8 +6607,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6455,8 +6684,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6557,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,8 +7021,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6853,8 +7098,11 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6927,8 +7175,11 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6999,6 +7250,9 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LAAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LAAB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>LAAB</t>
   </si>
@@ -656,121 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E7" s="2">
         <v>45260</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45169</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45077</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44985</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44895</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44804</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44712</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44620</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44530</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44439</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44347</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44255</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44165</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44074</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43982</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43890</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43799</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43708</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43616</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43524</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43434</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43343</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43251</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -846,8 +850,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -923,8 +930,11 @@
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1000,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1239,8 +1259,8 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
@@ -1254,14 +1274,17 @@
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,8 +1389,9 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1414,11 +1441,11 @@
         <v>0</v>
       </c>
       <c r="S17" s="3">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
         <v>38500</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
       <c r="U17" s="3">
         <v>0</v>
       </c>
@@ -1440,8 +1467,11 @@
       <c r="AA17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1491,11 +1521,11 @@
         <v>0</v>
       </c>
       <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>-38500</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
         <v>0</v>
       </c>
@@ -1517,8 +1547,11 @@
       <c r="AA18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,8 +1579,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1623,8 +1657,11 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1700,8 +1737,11 @@
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1748,37 +1788,40 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>4</v>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1825,20 +1868,20 @@
         <v>0</v>
       </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-38500</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
         <v>0</v>
       </c>
@@ -1854,8 +1897,11 @@
       <c r="AA23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1931,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,8 +2057,11 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2056,20 +2108,20 @@
         <v>0</v>
       </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-38500</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
         <v>0</v>
       </c>
@@ -2085,8 +2137,11 @@
       <c r="AA26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2133,20 +2188,20 @@
         <v>0</v>
       </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-38500</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
         <v>0</v>
       </c>
@@ -2162,8 +2217,11 @@
       <c r="AA27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2283,11 +2344,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,8 +2537,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2547,8 +2617,11 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2595,20 +2668,20 @@
         <v>0</v>
       </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-38500</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
         <v>0</v>
       </c>
@@ -2624,8 +2697,11 @@
       <c r="AA33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,8 +2777,11 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2749,20 +2828,20 @@
         <v>0</v>
       </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-38500</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
         <v>0</v>
       </c>
@@ -2778,90 +2857,96 @@
       <c r="AA35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E38" s="2">
         <v>45260</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45169</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45077</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44985</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44895</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44804</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44712</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44620</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44530</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44439</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44347</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44255</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44165</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44074</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43982</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43890</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43799</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43708</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43616</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43524</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43434</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43343</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43251</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,8 +3004,9 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2995,8 +3082,11 @@
       <c r="AA41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3072,8 +3162,11 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3149,8 +3242,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3226,8 +3322,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3303,8 +3402,11 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3380,8 +3482,11 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3457,8 +3562,11 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3534,8 +3642,11 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3575,8 +3686,8 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
@@ -3593,8 +3704,8 @@
       <c r="U49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,8 +4042,11 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,8 +4184,9 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4131,8 +4262,11 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4190,8 +4324,8 @@
       <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>4</v>
+      <c r="V58" s="3">
+        <v>100</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>4</v>
@@ -4208,8 +4342,11 @@
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4226,7 +4363,7 @@
         <v>200</v>
       </c>
       <c r="H59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3">
         <v>100</v>
@@ -4247,7 +4384,7 @@
         <v>100</v>
       </c>
       <c r="O59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -4268,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W59" s="3">
         <v>100</v>
@@ -4280,18 +4417,21 @@
         <v>100</v>
       </c>
       <c r="Z59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E60" s="3">
         <v>300</v>
@@ -4309,7 +4449,7 @@
         <v>300</v>
       </c>
       <c r="J60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K60" s="3">
         <v>200</v>
@@ -4333,7 +4473,7 @@
         <v>200</v>
       </c>
       <c r="R60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S60" s="3">
         <v>100</v>
@@ -4360,10 +4500,13 @@
         <v>100</v>
       </c>
       <c r="AA60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4439,8 +4582,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,13 +4902,16 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E66" s="3">
         <v>300</v>
@@ -4771,7 +4929,7 @@
         <v>300</v>
       </c>
       <c r="J66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K66" s="3">
         <v>200</v>
@@ -4795,7 +4953,7 @@
         <v>200</v>
       </c>
       <c r="R66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S66" s="3">
         <v>100</v>
@@ -4822,10 +4980,13 @@
         <v>100</v>
       </c>
       <c r="AA66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,8 +5332,11 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5173,7 +5347,7 @@
         <v>-39100</v>
       </c>
       <c r="F72" s="3">
-        <v>-39000</v>
+        <v>-39100</v>
       </c>
       <c r="G72" s="3">
         <v>-39000</v>
@@ -5191,7 +5365,7 @@
         <v>-39000</v>
       </c>
       <c r="L72" s="3">
-        <v>-38900</v>
+        <v>-39000</v>
       </c>
       <c r="M72" s="3">
         <v>-38900</v>
@@ -5209,13 +5383,13 @@
         <v>-38900</v>
       </c>
       <c r="R72" s="3">
-        <v>-38800</v>
+        <v>-38900</v>
       </c>
       <c r="S72" s="3">
         <v>-38800</v>
       </c>
       <c r="T72" s="3">
-        <v>-200</v>
+        <v>-38800</v>
       </c>
       <c r="U72" s="3">
         <v>-200</v>
@@ -5227,7 +5401,7 @@
         <v>-200</v>
       </c>
       <c r="X72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Y72" s="3">
         <v>-100</v>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,13 +5652,16 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E76" s="3">
         <v>-300</v>
@@ -5493,7 +5679,7 @@
         <v>-300</v>
       </c>
       <c r="J76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="K76" s="3">
         <v>-200</v>
@@ -5517,7 +5703,7 @@
         <v>-200</v>
       </c>
       <c r="R76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="S76" s="3">
         <v>-100</v>
@@ -5541,13 +5727,16 @@
         <v>-100</v>
       </c>
       <c r="Z76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,90 +5812,96 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E80" s="2">
         <v>45260</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45169</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45077</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44985</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44895</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44804</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44712</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44620</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44530</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44439</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44347</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44255</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44165</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44074</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43982</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43890</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43799</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43708</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43616</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43524</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43434</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43343</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43251</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5753,20 +5948,20 @@
         <v>0</v>
       </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-38500</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
         <v>0</v>
       </c>
@@ -5782,8 +5977,11 @@
       <c r="AA81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,8 +6009,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,8 +6487,11 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6350,8 +6567,11 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6599,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,8 +6837,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,8 +7267,11 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7101,8 +7347,11 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7178,8 +7427,11 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7253,6 +7505,9 @@
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LAAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LAAB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>LAAB</t>
   </si>
@@ -656,125 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E7" s="2">
         <v>45351</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45260</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45169</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45077</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44985</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44895</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44804</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44712</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44620</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44530</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44439</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44347</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44255</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44165</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44074</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43982</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43890</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43799</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43708</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43616</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43524</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43434</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43343</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43251</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -853,8 +857,11 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -933,8 +940,11 @@
       <c r="AB9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1013,8 +1023,11 @@
       <c r="AB10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,8 +1220,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1262,8 +1282,8 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>4</v>
@@ -1277,14 +1297,17 @@
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,8 +1416,9 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1444,11 +1471,11 @@
         <v>0</v>
       </c>
       <c r="T17" s="3">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3">
         <v>38500</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
       <c r="V17" s="3">
         <v>0</v>
       </c>
@@ -1470,8 +1497,11 @@
       <c r="AB17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1524,11 +1554,11 @@
         <v>0</v>
       </c>
       <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
         <v>-38500</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
         <v>0</v>
       </c>
@@ -1550,8 +1580,11 @@
       <c r="AB18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,8 +1613,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1660,8 +1694,11 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1740,8 +1777,11 @@
       <c r="AB21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1791,37 +1831,40 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>4</v>
+      <c r="Z22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1871,20 +1914,20 @@
         <v>0</v>
       </c>
       <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-38500</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
       <c r="X23" s="3">
         <v>0</v>
       </c>
@@ -1900,8 +1943,11 @@
       <c r="AB23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1980,8 +2026,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,8 +2109,11 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2111,20 +2163,20 @@
         <v>0</v>
       </c>
       <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-38500</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
       <c r="X26" s="3">
         <v>0</v>
       </c>
@@ -2140,8 +2192,11 @@
       <c r="AB26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2191,20 +2246,20 @@
         <v>0</v>
       </c>
       <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-38500</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
       <c r="X27" s="3">
         <v>0</v>
       </c>
@@ -2220,8 +2275,11 @@
       <c r="AB27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2347,11 +2408,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,8 +2607,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2620,8 +2690,11 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2671,20 +2744,20 @@
         <v>0</v>
       </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-38500</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
         <v>0</v>
       </c>
@@ -2700,8 +2773,11 @@
       <c r="AB33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,8 +2856,11 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2831,20 +2910,20 @@
         <v>0</v>
       </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-38500</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
         <v>0</v>
       </c>
@@ -2860,93 +2939,99 @@
       <c r="AB35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E38" s="2">
         <v>45351</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45260</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45169</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45077</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44985</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44895</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44804</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44712</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44620</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44530</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44439</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44347</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44255</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44165</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44074</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43982</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43890</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43799</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43708</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43616</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43524</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43434</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43343</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43251</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,8 +3091,9 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3085,8 +3172,11 @@
       <c r="AB41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3165,8 +3255,11 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3245,8 +3338,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3325,8 +3421,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3405,8 +3504,11 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3485,8 +3587,11 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3565,8 +3670,11 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3645,8 +3753,11 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3689,8 +3800,8 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>4</v>
@@ -3707,8 +3818,8 @@
       <c r="V49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,8 +4002,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,8 +4168,11 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,8 +4315,9 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4265,8 +4396,11 @@
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4327,8 +4461,8 @@
       <c r="V58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
+      <c r="W58" s="3">
+        <v>100</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>4</v>
@@ -4345,8 +4479,11 @@
       <c r="AB58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4366,7 +4503,7 @@
         <v>200</v>
       </c>
       <c r="I59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J59" s="3">
         <v>100</v>
@@ -4387,7 +4524,7 @@
         <v>100</v>
       </c>
       <c r="P59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
@@ -4408,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="W59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X59" s="3">
         <v>100</v>
@@ -4420,13 +4557,16 @@
         <v>100</v>
       </c>
       <c r="AA59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4434,7 +4574,7 @@
         <v>400</v>
       </c>
       <c r="E60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F60" s="3">
         <v>300</v>
@@ -4452,7 +4592,7 @@
         <v>300</v>
       </c>
       <c r="K60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L60" s="3">
         <v>200</v>
@@ -4476,7 +4616,7 @@
         <v>200</v>
       </c>
       <c r="S60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T60" s="3">
         <v>100</v>
@@ -4503,10 +4643,13 @@
         <v>100</v>
       </c>
       <c r="AB60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4585,8 +4728,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,8 +5060,11 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4914,7 +5072,7 @@
         <v>400</v>
       </c>
       <c r="E66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F66" s="3">
         <v>300</v>
@@ -4932,7 +5090,7 @@
         <v>300</v>
       </c>
       <c r="K66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L66" s="3">
         <v>200</v>
@@ -4956,7 +5114,7 @@
         <v>200</v>
       </c>
       <c r="S66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T66" s="3">
         <v>100</v>
@@ -4983,10 +5141,13 @@
         <v>100</v>
       </c>
       <c r="AB66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AC66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,8 +5506,11 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5350,7 +5524,7 @@
         <v>-39100</v>
       </c>
       <c r="G72" s="3">
-        <v>-39000</v>
+        <v>-39100</v>
       </c>
       <c r="H72" s="3">
         <v>-39000</v>
@@ -5368,7 +5542,7 @@
         <v>-39000</v>
       </c>
       <c r="M72" s="3">
-        <v>-38900</v>
+        <v>-39000</v>
       </c>
       <c r="N72" s="3">
         <v>-38900</v>
@@ -5386,13 +5560,13 @@
         <v>-38900</v>
       </c>
       <c r="S72" s="3">
-        <v>-38800</v>
+        <v>-38900</v>
       </c>
       <c r="T72" s="3">
         <v>-38800</v>
       </c>
       <c r="U72" s="3">
-        <v>-200</v>
+        <v>-38800</v>
       </c>
       <c r="V72" s="3">
         <v>-200</v>
@@ -5404,7 +5578,7 @@
         <v>-200</v>
       </c>
       <c r="Y72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Z72" s="3">
         <v>-100</v>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,8 +5838,11 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -5664,7 +5850,7 @@
         <v>-400</v>
       </c>
       <c r="E76" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="F76" s="3">
         <v>-300</v>
@@ -5682,7 +5868,7 @@
         <v>-300</v>
       </c>
       <c r="K76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="L76" s="3">
         <v>-200</v>
@@ -5706,7 +5892,7 @@
         <v>-200</v>
       </c>
       <c r="S76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="T76" s="3">
         <v>-100</v>
@@ -5730,13 +5916,16 @@
         <v>-100</v>
       </c>
       <c r="AA76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,93 +6004,99 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E80" s="2">
         <v>45351</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45260</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45169</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45077</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44985</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44895</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44804</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44712</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44620</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44530</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44439</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44347</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44255</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44165</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44074</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43982</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43890</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43799</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43708</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43616</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43524</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43434</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43343</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43251</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5951,20 +6146,20 @@
         <v>0</v>
       </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-38500</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
         <v>0</v>
       </c>
@@ -5980,8 +6175,11 @@
       <c r="AB81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6208,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,8 +6704,11 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6570,8 +6787,11 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +6820,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,8 +7067,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,8 +7513,11 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7350,8 +7596,11 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7430,8 +7679,11 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7508,6 +7760,9 @@
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>
